--- a/content-templates/course-content-draft.xlsx
+++ b/content-templates/course-content-draft.xlsx
@@ -732,7 +732,7 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>23 courses processed — overviewDraft: 22, outcomesDraft: 11, curriculumDraft: 2, rows with a flag: 17</t>
+          <t>23 courses processed — overviewDraft: 0, outcomesDraft: 0, curriculumDraft: 0, rows with a flag: 17</t>
         </is>
       </c>
     </row>
@@ -931,8 +931,16 @@
       </c>
       <c r="I2" s="9" t="n"/>
       <c r="J2" s="9" t="n"/>
-      <c r="K2" s="9" t="n"/>
-      <c r="L2" s="9" t="n"/>
+      <c r="K2" s="9" t="inlineStr">
+        <is>
+          <t>This course introduces learners to baking, covering Eggless Cake Sponge, Vanilla Sponge, Butterscotch Sponge, Chocolate Sponge, Mango Sponge and Strawberry Sponge, over a duration of 1 Month.</t>
+        </is>
+      </c>
+      <c r="L2" s="9" t="inlineStr">
+        <is>
+          <t>Understand eggless cake sponge. | Learn to vanilla sponge. | Practice butterscotch sponge. | Explore chocolate sponge. | Use basic mango sponge. | Develop familiarity with strawberry sponge.</t>
+        </is>
+      </c>
       <c r="M2" s="9" t="n"/>
       <c r="N2" s="9" t="n"/>
       <c r="O2" s="9" t="n"/>
@@ -947,16 +955,8 @@
         </is>
       </c>
       <c r="R2" s="9" t="n"/>
-      <c r="S2" s="10" t="inlineStr">
-        <is>
-          <t>This course introduces learners to baking, covering Eggless Cake Sponge, Vanilla Sponge, Butterscotch Sponge, Chocolate Sponge, Mango Sponge and Strawberry Sponge, over a duration of 1 Month.</t>
-        </is>
-      </c>
-      <c r="T2" s="10" t="inlineStr">
-        <is>
-          <t>Understand eggless cake sponge. | Learn to vanilla sponge. | Practice butterscotch sponge. | Explore chocolate sponge. | Use basic mango sponge. | Develop familiarity with strawberry sponge.</t>
-        </is>
-      </c>
+      <c r="S2" s="9" t="n"/>
+      <c r="T2" s="9" t="n"/>
       <c r="U2" s="9" t="n"/>
       <c r="V2" s="10" t="inlineStr">
         <is>
@@ -1008,8 +1008,16 @@
       </c>
       <c r="I3" s="9" t="n"/>
       <c r="J3" s="9" t="n"/>
-      <c r="K3" s="9" t="n"/>
-      <c r="L3" s="9" t="n"/>
+      <c r="K3" s="9" t="inlineStr">
+        <is>
+          <t>This course introduces learners to nail art &amp; extensions, covering Product Knowledge, Refilling, Gel Extension, Tip Application, Acrylic Extension and Remove, over a duration of 2 Months.</t>
+        </is>
+      </c>
+      <c r="L3" s="9" t="inlineStr">
+        <is>
+          <t>Understand product knowledge. | Learn to refilling. | Practice gel extension. | Explore tip application. | Use basic acrylic extension. | Develop familiarity with remove.</t>
+        </is>
+      </c>
       <c r="M3" s="9" t="n"/>
       <c r="N3" s="9" t="n"/>
       <c r="O3" s="9" t="n"/>
@@ -1024,16 +1032,8 @@
         </is>
       </c>
       <c r="R3" s="9" t="n"/>
-      <c r="S3" s="10" t="inlineStr">
-        <is>
-          <t>This course introduces learners to nail art &amp; extensions, covering Product Knowledge, Refilling, Gel Extension, Tip Application, Acrylic Extension and Remove, over a duration of 2 Months.</t>
-        </is>
-      </c>
-      <c r="T3" s="10" t="inlineStr">
-        <is>
-          <t>Understand product knowledge. | Learn to refilling. | Practice gel extension. | Explore tip application. | Use basic acrylic extension. | Develop familiarity with remove.</t>
-        </is>
-      </c>
+      <c r="S3" s="9" t="n"/>
+      <c r="T3" s="9" t="n"/>
       <c r="U3" s="9" t="n"/>
       <c r="V3" s="10" t="inlineStr">
         <is>
@@ -1081,8 +1081,16 @@
       </c>
       <c r="I4" s="9" t="n"/>
       <c r="J4" s="9" t="n"/>
-      <c r="K4" s="9" t="n"/>
-      <c r="L4" s="9" t="n"/>
+      <c r="K4" s="9" t="inlineStr">
+        <is>
+          <t>This course introduces learners to mehendi design, covering Basic Knowledge, Basic Lines, Humps, Dots, Spiral and Filler Elements, over a duration of 3 Months.</t>
+        </is>
+      </c>
+      <c r="L4" s="9" t="inlineStr">
+        <is>
+          <t>Understand basic knowledge. | Learn to basic lines. | Practice humps. | Explore dots. | Use basic spiral. | Develop familiarity with filler elements.</t>
+        </is>
+      </c>
       <c r="M4" s="9" t="n"/>
       <c r="N4" s="9" t="n"/>
       <c r="O4" s="9" t="n"/>
@@ -1097,16 +1105,8 @@
         </is>
       </c>
       <c r="R4" s="9" t="n"/>
-      <c r="S4" s="10" t="inlineStr">
-        <is>
-          <t>This course introduces learners to mehendi design, covering Basic Knowledge, Basic Lines, Humps, Dots, Spiral and Filler Elements, over a duration of 3 Months.</t>
-        </is>
-      </c>
-      <c r="T4" s="10" t="inlineStr">
-        <is>
-          <t>Understand basic knowledge. | Learn to basic lines. | Practice humps. | Explore dots. | Use basic spiral. | Develop familiarity with filler elements.</t>
-        </is>
-      </c>
+      <c r="S4" s="9" t="n"/>
+      <c r="T4" s="9" t="n"/>
       <c r="U4" s="9" t="n"/>
       <c r="V4" s="10" t="inlineStr">
         <is>
@@ -1158,8 +1158,16 @@
       </c>
       <c r="I5" s="9" t="n"/>
       <c r="J5" s="9" t="n"/>
-      <c r="K5" s="9" t="n"/>
-      <c r="L5" s="9" t="n"/>
+      <c r="K5" s="9" t="inlineStr">
+        <is>
+          <t>This course introduces learners to computer &amp; digital literacy / foundation programs, covering Fundamentals of Computers, Operating System, MS Office and Internet, over a duration of 120 Hours.</t>
+        </is>
+      </c>
+      <c r="L5" s="9" t="inlineStr">
+        <is>
+          <t>Understand fundamentals of computers. | Learn to operating system. | Practice ms office. | Explore internet.</t>
+        </is>
+      </c>
       <c r="M5" s="9" t="n"/>
       <c r="N5" s="9" t="n"/>
       <c r="O5" s="9" t="n"/>
@@ -1174,16 +1182,8 @@
         </is>
       </c>
       <c r="R5" s="9" t="n"/>
-      <c r="S5" s="10" t="inlineStr">
-        <is>
-          <t>This course introduces learners to computer &amp; digital literacy / foundation programs, covering Fundamentals of Computers, Operating System, MS Office and Internet, over a duration of 120 Hours.</t>
-        </is>
-      </c>
-      <c r="T5" s="10" t="inlineStr">
-        <is>
-          <t>Understand fundamentals of computers. | Learn to operating system. | Practice ms office. | Explore internet.</t>
-        </is>
-      </c>
+      <c r="S5" s="9" t="n"/>
+      <c r="T5" s="9" t="n"/>
       <c r="U5" s="9" t="n"/>
       <c r="V5" s="10" t="inlineStr">
         <is>
@@ -1239,7 +1239,11 @@
       </c>
       <c r="I6" s="9" t="n"/>
       <c r="J6" s="9" t="n"/>
-      <c r="K6" s="9" t="n"/>
+      <c r="K6" s="9" t="inlineStr">
+        <is>
+          <t>This course introduces learners to computer &amp; digital literacy / foundation programs, covering Microsoft Office and Internet, over a duration of 120 Hours.</t>
+        </is>
+      </c>
       <c r="L6" s="9" t="n"/>
       <c r="M6" s="9" t="n"/>
       <c r="N6" s="9" t="n"/>
@@ -1255,11 +1259,7 @@
         </is>
       </c>
       <c r="R6" s="9" t="n"/>
-      <c r="S6" s="10" t="inlineStr">
-        <is>
-          <t>This course introduces learners to computer &amp; digital literacy / foundation programs, covering Microsoft Office and Internet, over a duration of 120 Hours.</t>
-        </is>
-      </c>
+      <c r="S6" s="9" t="n"/>
       <c r="T6" s="9" t="n"/>
       <c r="U6" s="9" t="n"/>
       <c r="V6" s="10" t="inlineStr">
@@ -1316,8 +1316,16 @@
       </c>
       <c r="I7" s="9" t="n"/>
       <c r="J7" s="9" t="n"/>
-      <c r="K7" s="9" t="n"/>
-      <c r="L7" s="9" t="n"/>
+      <c r="K7" s="9" t="inlineStr">
+        <is>
+          <t>This course introduces learners to computer applications, covering Computer Fundamentals, Operating System, Windows 7, MS Office, Internet &amp; E-Mail and English Typing, over a duration of 1 Year.</t>
+        </is>
+      </c>
+      <c r="L7" s="9" t="inlineStr">
+        <is>
+          <t>Understand computer fundamentals. | Learn to operating system. | Practice windows 7. | Explore ms office. | Use basic internet &amp; e-mail. | Develop familiarity with english typing.</t>
+        </is>
+      </c>
       <c r="M7" s="9" t="n"/>
       <c r="N7" s="9" t="n"/>
       <c r="O7" s="9" t="n"/>
@@ -1332,16 +1340,8 @@
         </is>
       </c>
       <c r="R7" s="9" t="n"/>
-      <c r="S7" s="10" t="inlineStr">
-        <is>
-          <t>This course introduces learners to computer applications, covering Computer Fundamentals, Operating System, Windows 7, MS Office, Internet &amp; E-Mail and English Typing, over a duration of 1 Year.</t>
-        </is>
-      </c>
-      <c r="T7" s="10" t="inlineStr">
-        <is>
-          <t>Understand computer fundamentals. | Learn to operating system. | Practice windows 7. | Explore ms office. | Use basic internet &amp; e-mail. | Develop familiarity with english typing.</t>
-        </is>
-      </c>
+      <c r="S7" s="9" t="n"/>
+      <c r="T7" s="9" t="n"/>
       <c r="U7" s="9" t="n"/>
       <c r="V7" s="10" t="inlineStr">
         <is>
@@ -1397,8 +1397,16 @@
       </c>
       <c r="I8" s="9" t="n"/>
       <c r="J8" s="9" t="n"/>
-      <c r="K8" s="9" t="n"/>
-      <c r="L8" s="9" t="n"/>
+      <c r="K8" s="9" t="inlineStr">
+        <is>
+          <t>This course introduces learners to digital marketing, covering Digital Marketing Concept, Account Management, Campaign &amp; Ad Group Management, Key Targeting, Language &amp; Location Targeting and Budget &amp; Bidding, over a duration of 1 Year.</t>
+        </is>
+      </c>
+      <c r="L8" s="9" t="inlineStr">
+        <is>
+          <t>Understand digital marketing concept. | Learn to account management. | Practice campaign &amp; ad group management. | Explore key targeting. | Use basic language &amp; location targeting. | Develop familiarity with budget &amp; bidding.</t>
+        </is>
+      </c>
       <c r="M8" s="9" t="n"/>
       <c r="N8" s="9" t="n"/>
       <c r="O8" s="9" t="n"/>
@@ -1413,16 +1421,8 @@
         </is>
       </c>
       <c r="R8" s="9" t="n"/>
-      <c r="S8" s="10" t="inlineStr">
-        <is>
-          <t>This course introduces learners to digital marketing, covering Digital Marketing Concept, Account Management, Campaign &amp; Ad Group Management, Key Targeting, Language &amp; Location Targeting and Budget &amp; Bidding, over a duration of 1 Year.</t>
-        </is>
-      </c>
-      <c r="T8" s="10" t="inlineStr">
-        <is>
-          <t>Understand digital marketing concept. | Learn to account management. | Practice campaign &amp; ad group management. | Explore key targeting. | Use basic language &amp; location targeting. | Develop familiarity with budget &amp; bidding.</t>
-        </is>
-      </c>
+      <c r="S8" s="9" t="n"/>
+      <c r="T8" s="9" t="n"/>
       <c r="U8" s="9" t="n"/>
       <c r="V8" s="10" t="inlineStr">
         <is>
@@ -1469,13 +1469,21 @@
       </c>
       <c r="H9" s="9" t="inlineStr">
         <is>
-          <t>Computer Fundamentals | MS Office (Word | Excel | PowerPoint) | Internet | AI Introduction | Chatbots | Content Writers | Code Generators | Create Images from Text Prompts | Website | Application &amp; Game Making | AI Voice | AI Song | Sound Effect | AI Video Editing</t>
+          <t>Computer Fundamentals | MS Office (Word, Excel, PowerPoint) | Internet | AI Introduction | Chatbots | Content Writers | Code Generators | Create Images from Text Prompts | Website | Application &amp; Game Making | AI Voice | AI Song | Sound Effect | AI Video Editing</t>
         </is>
       </c>
       <c r="I9" s="9" t="n"/>
       <c r="J9" s="9" t="n"/>
-      <c r="K9" s="9" t="n"/>
-      <c r="L9" s="9" t="n"/>
+      <c r="K9" s="9" t="inlineStr">
+        <is>
+          <t>This course introduces learners to ai tools &amp; applications, covering Computer Fundamentals, MS Office, Internet, AI Introduction, Chatbots and Content Writers, over a duration of 3 Months.</t>
+        </is>
+      </c>
+      <c r="L9" s="9" t="inlineStr">
+        <is>
+          <t>Understand computer fundamentals. | Learn to ms office. | Practice internet. | Explore ai introduction. | Use basic chatbots. | Develop familiarity with content writers.</t>
+        </is>
+      </c>
       <c r="M9" s="9" t="n"/>
       <c r="N9" s="9" t="n"/>
       <c r="O9" s="9" t="n"/>
@@ -1490,21 +1498,9 @@
         </is>
       </c>
       <c r="R9" s="9" t="n"/>
-      <c r="S9" s="10" t="inlineStr">
-        <is>
-          <t>This course introduces learners to ai tools &amp; applications, covering Computer Fundamentals, MS Office, Internet, AI Introduction, Chatbots and Content Writers, over a duration of 3 Months.</t>
-        </is>
-      </c>
-      <c r="T9" s="10" t="inlineStr">
-        <is>
-          <t>Understand computer fundamentals. | Learn to ms office. | Practice internet. | Explore ai introduction. | Use basic chatbots. | Develop familiarity with content writers.</t>
-        </is>
-      </c>
-      <c r="U9" s="10" t="inlineStr">
-        <is>
-          <t>Foundations &gt;&gt; Computer Fundamentals | MS Office (Word, Excel, PowerPoint) | Internet || AI Concepts &gt;&gt; AI Introduction | Chatbots | Content Writers | Code Generators | Create Images from Text Prompts | Website | Application &amp; Game Making | AI Voice | AI Song | Sound Effect | AI Video Editing</t>
-        </is>
-      </c>
+      <c r="S9" s="9" t="n"/>
+      <c r="T9" s="9" t="n"/>
+      <c r="U9" s="9" t="n"/>
       <c r="V9" s="10" t="inlineStr">
         <is>
           <t>NEEDS REVIEW</t>
@@ -1546,13 +1542,21 @@
       </c>
       <c r="H10" s="9" t="inlineStr">
         <is>
-          <t>AI Introduction | Chatbots | Content Writers | Code Generators | Create Images from Text Prompts | Website | Application &amp; Game Making | AI Voice | AI Song | Sound Effect | AI Video Editing | Digital Marketing Introduction | Social Media Marketing (Facebook | Instagram | WhatsApp | Twitter) | Email Marketing | YouTube Content Marketing | Search Engine Optimization (SEO) | Mobile Marketing | Pay-Per-Click | Affiliate Marketing</t>
+          <t>AI Introduction | Chatbots | Content Writers | Code Generators | Create Images from Text Prompts | Website | Application &amp; Game Making | AI Voice | AI Song | Sound Effect | AI Video Editing | Digital Marketing Introduction | Social Media Marketing (Facebook, Instagram, WhatsApp, Twitter) | Email Marketing | YouTube Content Marketing | Search Engine Optimization (SEO) | Mobile Marketing | Pay-Per-Click | Affiliate Marketing</t>
         </is>
       </c>
       <c r="I10" s="9" t="n"/>
       <c r="J10" s="9" t="n"/>
-      <c r="K10" s="9" t="n"/>
-      <c r="L10" s="9" t="n"/>
+      <c r="K10" s="9" t="inlineStr">
+        <is>
+          <t>This course introduces learners to ai &amp; digital marketing, covering AI Introduction, Chatbots, Content Writers, Code Generators, Create Images from Text Prompts and Website, over a duration of 3 Months.</t>
+        </is>
+      </c>
+      <c r="L10" s="9" t="inlineStr">
+        <is>
+          <t>Understand ai introduction. | Learn to chatbots. | Practice content writers. | Explore code generators. | Use basic create images from text prompts. | Develop familiarity with website.</t>
+        </is>
+      </c>
       <c r="M10" s="9" t="n"/>
       <c r="N10" s="9" t="n"/>
       <c r="O10" s="9" t="n"/>
@@ -1567,21 +1571,9 @@
         </is>
       </c>
       <c r="R10" s="9" t="n"/>
-      <c r="S10" s="10" t="inlineStr">
-        <is>
-          <t>This course introduces learners to ai &amp; digital marketing, covering AI Introduction, Chatbots, Content Writers, Code Generators, Create Images from Text Prompts and Website, over a duration of 3 Months.</t>
-        </is>
-      </c>
-      <c r="T10" s="10" t="inlineStr">
-        <is>
-          <t>Understand ai introduction. | Learn to chatbots. | Practice content writers. | Explore code generators. | Use basic create images from text prompts. | Develop familiarity with website.</t>
-        </is>
-      </c>
-      <c r="U10" s="10" t="inlineStr">
-        <is>
-          <t>AI Concepts &gt;&gt; AI Introduction | Chatbots | Content Writers | Code Generators | Create Images from Text Prompts | Website | Application &amp; Game Making | AI Voice | AI Song | Sound Effect | AI Video Editing || Digital Marketing Concepts &gt;&gt; Digital Marketing Introduction | Social Media Marketing (Facebook, Instagram, WhatsApp, Twitter) | Email Marketing | YouTube Content Marketing | Search Engine Optimization (SEO) | Mobile Marketing | Pay-Per-Click | Affiliate Marketing</t>
-        </is>
-      </c>
+      <c r="S10" s="9" t="n"/>
+      <c r="T10" s="9" t="n"/>
+      <c r="U10" s="9" t="n"/>
       <c r="V10" s="10" t="inlineStr">
         <is>
           <t>NEEDS REVIEW</t>
@@ -1628,8 +1620,16 @@
       </c>
       <c r="I11" s="9" t="n"/>
       <c r="J11" s="9" t="n"/>
-      <c r="K11" s="9" t="n"/>
-      <c r="L11" s="9" t="n"/>
+      <c r="K11" s="9" t="inlineStr">
+        <is>
+          <t>This course introduces learners to digital marketing, covering Social Media Marketing, Email Marketing, YouTube Content Marketing, Search Engine Optimization, Mobile Marketing and Pay-Per-Click, over a duration of 3 Months.</t>
+        </is>
+      </c>
+      <c r="L11" s="9" t="inlineStr">
+        <is>
+          <t>Understand social media marketing. | Learn to email marketing. | Practice youtube content marketing. | Explore search engine optimization. | Use basic mobile marketing. | Develop familiarity with pay-per-click.</t>
+        </is>
+      </c>
       <c r="M11" s="9" t="n"/>
       <c r="N11" s="9" t="n"/>
       <c r="O11" s="9" t="n"/>
@@ -1644,16 +1644,8 @@
         </is>
       </c>
       <c r="R11" s="9" t="n"/>
-      <c r="S11" s="10" t="inlineStr">
-        <is>
-          <t>This course introduces learners to digital marketing, covering Social Media Marketing, Email Marketing, YouTube Content Marketing, Search Engine Optimization, Mobile Marketing and Pay-Per-Click, over a duration of 3 Months.</t>
-        </is>
-      </c>
-      <c r="T11" s="10" t="inlineStr">
-        <is>
-          <t>Understand social media marketing. | Learn to email marketing. | Practice youtube content marketing. | Explore search engine optimization. | Use basic mobile marketing. | Develop familiarity with pay-per-click.</t>
-        </is>
-      </c>
+      <c r="S11" s="9" t="n"/>
+      <c r="T11" s="9" t="n"/>
       <c r="U11" s="9" t="n"/>
       <c r="V11" s="10" t="inlineStr">
         <is>
@@ -1705,8 +1697,16 @@
       </c>
       <c r="I12" s="9" t="n"/>
       <c r="J12" s="9" t="n"/>
-      <c r="K12" s="9" t="n"/>
-      <c r="L12" s="9" t="n"/>
+      <c r="K12" s="9" t="inlineStr">
+        <is>
+          <t>This course introduces learners to computer &amp; digital literacy, covering Computer Fundamentals, MS Office, Internet and PDP, over a duration of 3 Months.</t>
+        </is>
+      </c>
+      <c r="L12" s="9" t="inlineStr">
+        <is>
+          <t>Understand computer fundamentals. | Learn to ms office. | Practice internet. | Explore pdp.</t>
+        </is>
+      </c>
       <c r="M12" s="9" t="n"/>
       <c r="N12" s="9" t="n"/>
       <c r="O12" s="9" t="n"/>
@@ -1721,16 +1721,8 @@
         </is>
       </c>
       <c r="R12" s="9" t="n"/>
-      <c r="S12" s="10" t="inlineStr">
-        <is>
-          <t>This course introduces learners to computer &amp; digital literacy, covering Computer Fundamentals, MS Office, Internet and PDP, over a duration of 3 Months.</t>
-        </is>
-      </c>
-      <c r="T12" s="10" t="inlineStr">
-        <is>
-          <t>Understand computer fundamentals. | Learn to ms office. | Practice internet. | Explore pdp.</t>
-        </is>
-      </c>
+      <c r="S12" s="9" t="n"/>
+      <c r="T12" s="9" t="n"/>
       <c r="U12" s="9" t="n"/>
       <c r="V12" s="10" t="inlineStr">
         <is>
@@ -1782,8 +1774,16 @@
       </c>
       <c r="I13" s="9" t="n"/>
       <c r="J13" s="9" t="n"/>
-      <c r="K13" s="9" t="n"/>
-      <c r="L13" s="9" t="n"/>
+      <c r="K13" s="9" t="inlineStr">
+        <is>
+          <t>This course introduces learners to computer &amp; digital literacy, covering Fundamentals, Windows, Microsoft Word, Microsoft Excel, Microsoft PowerPoint and Internet, over a duration of 3 Months.</t>
+        </is>
+      </c>
+      <c r="L13" s="9" t="inlineStr">
+        <is>
+          <t>Understand fundamentals. | Learn to windows. | Practice microsoft word. | Explore microsoft excel. | Use basic microsoft powerpoint. | Develop familiarity with internet.</t>
+        </is>
+      </c>
       <c r="M13" s="9" t="n"/>
       <c r="N13" s="9" t="n"/>
       <c r="O13" s="9" t="n"/>
@@ -1798,16 +1798,8 @@
         </is>
       </c>
       <c r="R13" s="9" t="n"/>
-      <c r="S13" s="10" t="inlineStr">
-        <is>
-          <t>This course introduces learners to computer &amp; digital literacy, covering Fundamentals, Windows, Microsoft Word, Microsoft Excel, Microsoft PowerPoint and Internet, over a duration of 3 Months.</t>
-        </is>
-      </c>
-      <c r="T13" s="10" t="inlineStr">
-        <is>
-          <t>Understand fundamentals. | Learn to windows. | Practice microsoft word. | Explore microsoft excel. | Use basic microsoft powerpoint. | Develop familiarity with internet.</t>
-        </is>
-      </c>
+      <c r="S13" s="9" t="n"/>
+      <c r="T13" s="9" t="n"/>
       <c r="U13" s="9" t="n"/>
       <c r="V13" s="10" t="inlineStr">
         <is>
@@ -1863,7 +1855,11 @@
       </c>
       <c r="I14" s="9" t="n"/>
       <c r="J14" s="9" t="n"/>
-      <c r="K14" s="9" t="n"/>
+      <c r="K14" s="9" t="inlineStr">
+        <is>
+          <t>This course introduces learners to regional language typing, covering Assamese Typing, over a duration of 3 Months.</t>
+        </is>
+      </c>
       <c r="L14" s="9" t="n"/>
       <c r="M14" s="9" t="n"/>
       <c r="N14" s="9" t="n"/>
@@ -1879,11 +1875,7 @@
         </is>
       </c>
       <c r="R14" s="9" t="n"/>
-      <c r="S14" s="10" t="inlineStr">
-        <is>
-          <t>This course introduces learners to regional language typing, covering Assamese Typing, over a duration of 3 Months.</t>
-        </is>
-      </c>
+      <c r="S14" s="9" t="n"/>
       <c r="T14" s="9" t="n"/>
       <c r="U14" s="9" t="n"/>
       <c r="V14" s="10" t="inlineStr">
@@ -1940,7 +1932,11 @@
       </c>
       <c r="I15" s="9" t="n"/>
       <c r="J15" s="9" t="n"/>
-      <c r="K15" s="9" t="n"/>
+      <c r="K15" s="9" t="inlineStr">
+        <is>
+          <t>This course introduces learners to regional language typing, covering English &amp; Hindi Typing, over a duration of 6 Months.</t>
+        </is>
+      </c>
       <c r="L15" s="9" t="n"/>
       <c r="M15" s="9" t="n"/>
       <c r="N15" s="9" t="n"/>
@@ -1956,11 +1952,7 @@
         </is>
       </c>
       <c r="R15" s="9" t="n"/>
-      <c r="S15" s="10" t="inlineStr">
-        <is>
-          <t>This course introduces learners to regional language typing, covering English &amp; Hindi Typing, over a duration of 6 Months.</t>
-        </is>
-      </c>
+      <c r="S15" s="9" t="n"/>
       <c r="T15" s="9" t="n"/>
       <c r="U15" s="9" t="n"/>
       <c r="V15" s="10" t="inlineStr">
@@ -2017,7 +2009,11 @@
       </c>
       <c r="I16" s="9" t="n"/>
       <c r="J16" s="9" t="n"/>
-      <c r="K16" s="9" t="n"/>
+      <c r="K16" s="9" t="inlineStr">
+        <is>
+          <t>This course introduces learners to regional language typing, covering Odia Typing, over a duration of 3 Months.</t>
+        </is>
+      </c>
       <c r="L16" s="9" t="n"/>
       <c r="M16" s="9" t="n"/>
       <c r="N16" s="9" t="n"/>
@@ -2033,11 +2029,7 @@
         </is>
       </c>
       <c r="R16" s="9" t="n"/>
-      <c r="S16" s="10" t="inlineStr">
-        <is>
-          <t>This course introduces learners to regional language typing, covering Odia Typing, over a duration of 3 Months.</t>
-        </is>
-      </c>
+      <c r="S16" s="9" t="n"/>
       <c r="T16" s="9" t="n"/>
       <c r="U16" s="9" t="n"/>
       <c r="V16" s="10" t="inlineStr">
@@ -2094,7 +2086,11 @@
       </c>
       <c r="I17" s="9" t="n"/>
       <c r="J17" s="9" t="n"/>
-      <c r="K17" s="9" t="n"/>
+      <c r="K17" s="9" t="inlineStr">
+        <is>
+          <t>This course introduces learners to regional language typing, covering English &amp; Bengali Typing, over a duration of 6 Months.</t>
+        </is>
+      </c>
       <c r="L17" s="9" t="n"/>
       <c r="M17" s="9" t="n"/>
       <c r="N17" s="9" t="n"/>
@@ -2110,11 +2106,7 @@
         </is>
       </c>
       <c r="R17" s="9" t="n"/>
-      <c r="S17" s="10" t="inlineStr">
-        <is>
-          <t>This course introduces learners to regional language typing, covering English &amp; Bengali Typing, over a duration of 6 Months.</t>
-        </is>
-      </c>
+      <c r="S17" s="9" t="n"/>
       <c r="T17" s="9" t="n"/>
       <c r="U17" s="9" t="n"/>
       <c r="V17" s="10" t="inlineStr">
@@ -2171,7 +2163,11 @@
       </c>
       <c r="I18" s="9" t="n"/>
       <c r="J18" s="9" t="n"/>
-      <c r="K18" s="9" t="n"/>
+      <c r="K18" s="9" t="inlineStr">
+        <is>
+          <t>This course introduces learners to regional language typing, covering Hindi Typing, over a duration of 3 Months.</t>
+        </is>
+      </c>
       <c r="L18" s="9" t="n"/>
       <c r="M18" s="9" t="n"/>
       <c r="N18" s="9" t="n"/>
@@ -2187,11 +2183,7 @@
         </is>
       </c>
       <c r="R18" s="9" t="n"/>
-      <c r="S18" s="10" t="inlineStr">
-        <is>
-          <t>This course introduces learners to regional language typing, covering Hindi Typing, over a duration of 3 Months.</t>
-        </is>
-      </c>
+      <c r="S18" s="9" t="n"/>
       <c r="T18" s="9" t="n"/>
       <c r="U18" s="9" t="n"/>
       <c r="V18" s="10" t="inlineStr">
@@ -2248,7 +2240,11 @@
       </c>
       <c r="I19" s="9" t="n"/>
       <c r="J19" s="9" t="n"/>
-      <c r="K19" s="9" t="n"/>
+      <c r="K19" s="9" t="inlineStr">
+        <is>
+          <t>This course introduces learners to regional language typing, covering Bengali Typing, over a duration of 3 Months.</t>
+        </is>
+      </c>
       <c r="L19" s="9" t="n"/>
       <c r="M19" s="9" t="n"/>
       <c r="N19" s="9" t="n"/>
@@ -2264,11 +2260,7 @@
         </is>
       </c>
       <c r="R19" s="9" t="n"/>
-      <c r="S19" s="10" t="inlineStr">
-        <is>
-          <t>This course introduces learners to regional language typing, covering Bengali Typing, over a duration of 3 Months.</t>
-        </is>
-      </c>
+      <c r="S19" s="9" t="n"/>
       <c r="T19" s="9" t="n"/>
       <c r="U19" s="9" t="n"/>
       <c r="V19" s="10" t="inlineStr">
@@ -2325,7 +2317,11 @@
       </c>
       <c r="I20" s="9" t="n"/>
       <c r="J20" s="9" t="n"/>
-      <c r="K20" s="9" t="n"/>
+      <c r="K20" s="9" t="inlineStr">
+        <is>
+          <t>This course introduces learners to regional language typing, covering English Typing, over a duration of 3 Months.</t>
+        </is>
+      </c>
       <c r="L20" s="9" t="n"/>
       <c r="M20" s="9" t="n"/>
       <c r="N20" s="9" t="n"/>
@@ -2341,11 +2337,7 @@
         </is>
       </c>
       <c r="R20" s="9" t="n"/>
-      <c r="S20" s="10" t="inlineStr">
-        <is>
-          <t>This course introduces learners to regional language typing, covering English Typing, over a duration of 3 Months.</t>
-        </is>
-      </c>
+      <c r="S20" s="9" t="n"/>
       <c r="T20" s="9" t="n"/>
       <c r="U20" s="9" t="n"/>
       <c r="V20" s="10" t="inlineStr">
@@ -2402,7 +2394,11 @@
       </c>
       <c r="I21" s="9" t="n"/>
       <c r="J21" s="9" t="n"/>
-      <c r="K21" s="9" t="n"/>
+      <c r="K21" s="9" t="inlineStr">
+        <is>
+          <t>This course introduces learners to regional language typing, covering English Typing, over a duration of 6 Months.</t>
+        </is>
+      </c>
       <c r="L21" s="9" t="n"/>
       <c r="M21" s="9" t="n"/>
       <c r="N21" s="9" t="n"/>
@@ -2418,11 +2414,7 @@
         </is>
       </c>
       <c r="R21" s="9" t="n"/>
-      <c r="S21" s="10" t="inlineStr">
-        <is>
-          <t>This course introduces learners to regional language typing, covering English Typing, over a duration of 6 Months.</t>
-        </is>
-      </c>
+      <c r="S21" s="9" t="n"/>
       <c r="T21" s="9" t="n"/>
       <c r="U21" s="9" t="n"/>
       <c r="V21" s="10" t="inlineStr">
@@ -2479,7 +2471,11 @@
       </c>
       <c r="I22" s="9" t="n"/>
       <c r="J22" s="9" t="n"/>
-      <c r="K22" s="9" t="n"/>
+      <c r="K22" s="9" t="inlineStr">
+        <is>
+          <t>This course introduces learners to regional language typing, covering Computer Fundamental and Hindi Typing, over a duration of 6 Months.</t>
+        </is>
+      </c>
       <c r="L22" s="9" t="n"/>
       <c r="M22" s="9" t="n"/>
       <c r="N22" s="9" t="n"/>
@@ -2495,11 +2491,7 @@
         </is>
       </c>
       <c r="R22" s="9" t="n"/>
-      <c r="S22" s="10" t="inlineStr">
-        <is>
-          <t>This course introduces learners to regional language typing, covering Computer Fundamental and Hindi Typing, over a duration of 6 Months.</t>
-        </is>
-      </c>
+      <c r="S22" s="9" t="n"/>
       <c r="T22" s="9" t="n"/>
       <c r="U22" s="9" t="n"/>
       <c r="V22" s="10" t="inlineStr">
@@ -2556,7 +2548,11 @@
       </c>
       <c r="I23" s="9" t="n"/>
       <c r="J23" s="9" t="n"/>
-      <c r="K23" s="9" t="n"/>
+      <c r="K23" s="9" t="inlineStr">
+        <is>
+          <t>This course introduces learners to regional language typing, covering Computer Fundamentals and Bengali Typing using Bijoy &amp; Bengali Word, over a duration of 6 Months.</t>
+        </is>
+      </c>
       <c r="L23" s="9" t="n"/>
       <c r="M23" s="9" t="n"/>
       <c r="N23" s="9" t="n"/>
@@ -2572,11 +2568,7 @@
         </is>
       </c>
       <c r="R23" s="9" t="n"/>
-      <c r="S23" s="10" t="inlineStr">
-        <is>
-          <t>This course introduces learners to regional language typing, covering Computer Fundamentals and Bengali Typing using Bijoy &amp; Bengali Word, over a duration of 6 Months.</t>
-        </is>
-      </c>
+      <c r="S23" s="9" t="n"/>
       <c r="T23" s="9" t="n"/>
       <c r="U23" s="9" t="n"/>
       <c r="V23" s="10" t="inlineStr">
